--- a/TestData/LV_TMTT0048664_VerifyWaiveRFOFieldInOpportunityEngagementCF.xlsx
+++ b/TestData/LV_TMTT0048664_VerifyWaiveRFOFieldInOpportunityEngagementCF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974C8745-1928-45C7-ACA5-E7A82E0A18BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CCDFB8-CF01-4E25-98AC-D0B6E03A9559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="AddContact" sheetId="14" r:id="rId5"/>
     <sheet name="ExistingOpp" sheetId="15" r:id="rId6"/>
     <sheet name="ExistingEng" sheetId="16" r:id="rId7"/>
+    <sheet name="ExistingNonCFOpp" sheetId="17" r:id="rId8"/>
+    <sheet name="NonCFUser" sheetId="18" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>James Craven</t>
   </si>
@@ -297,6 +299,33 @@
   </si>
   <si>
     <t>Opportunity_WaiveRFO</t>
+  </si>
+  <si>
+    <t>144835</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>FVA</t>
+  </si>
+  <si>
+    <t>Opportunity_NonWaiveRFO</t>
+  </si>
+  <si>
+    <t>137601</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>FR Financial User</t>
+  </si>
+  <si>
+    <t>Dimitri Drone</t>
   </si>
 </sst>
 </file>
@@ -1450,4 +1479,86 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A169423-43EA-4CBC-899C-8D731F1940FF}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F70DCAA-89F6-41D7-A953-C1C405A7E260}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>